--- a/DEPLOY-checklist.xlsx
+++ b/DEPLOY-checklist.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isi .env (nano .env). JWT_SECRET WAJIB diganti; DB_PASSWORD hanya berlaku saat volume DB dibuat pertama kali; NEXT_PUBLIC_API_URL dibakar saat build.</t>
+          <t xml:space="preserve">Isi .env (nano .env). JWT_SECRET WAJIB diganti; DB_PASSWORD hanya berlaku saat volume DB dibuat pertama kali; NEXT_PUBLIC_API_URL TIDAK perlu diisi (dasbor memanggil API lewat alamatnya sendiri).</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -728,8 +728,7 @@
 JWT_SECRET=&lt;hasil acak pertama&gt;
 DB_PASSWORD=&lt;hasil acak kedua&gt;
 OPENORCHESTRATOR_TZ=Asia/Jakarta
-CORS_ORIGINS=https://orchestrator.domainmu.com
-NEXT_PUBLIC_API_URL=https://api.orchestrator.domainmu.com</t>
+CORS_ORIGINS=https://orchestrator.domainmu.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1656,34 +1655,35 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login di dasbor gagal / error CORS</t>
+          <t xml:space="preserve">Login gagal: "Dasbor tidak bisa menghubungi backend"</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORS_ORIGINS tidak sama persis dengan alamat dasbor (termasuk https://).</t>
+          <t xml:space="preserve">Backend mati atau belum sehat.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perbaiki .env, lalu docker compose up -d</t>
+          <t xml:space="preserve">docker compose ps
+docker compose logs backend --tail 100</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dasbor memanggil alamat API yang salah</t>
+          <t xml:space="preserve">Login di dasbor gagal / error CORS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEXT_PUBLIC_API_URL salah (dibakar saat build).</t>
+          <t xml:space="preserve">Hanya kalau NEXT_PUBLIC_API_URL diisi: CORS_ORIGINS harus sama persis dengan alamat dasbor (termasuk https://).</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perbaiki .env, lalu docker compose up -d --build frontend</t>
+          <t xml:space="preserve">Kosongkan NEXT_PUBLIC_API_URL di .env, lalu docker compose up -d --build frontend</t>
         </is>
       </c>
     </row>
